--- a/output/full_scan/batch_seq0_2026-06-17.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-17.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8411</v>
+        <v>8358</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>726.1289068851501</v>
+        <v>739.0072009233414</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12.25</v>
+        <v>640</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.88806939892757</v>
+        <v>63.59562388202893</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.12632612633877</v>
+        <v>22.44568247945333</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8223380581409789</v>
+        <v>0.2589230051954571</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0153588617735058</v>
+        <v>-2.587117056290218</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8431</v>
+        <v>8411</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>712.7083163934456</v>
+        <v>726.1289068851501</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>58.8</v>
+        <v>12.25</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.98797904040639</v>
+        <v>53.88806939892757</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>17.16300388577919</v>
+        <v>33.12632612633877</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.877069088007528</v>
+        <v>0.8223380581409789</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.4900027713477177</v>
+        <v>0.0153588617735058</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8472</v>
+        <v>8431</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>707.208206471732</v>
+        <v>712.7083163934456</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.39437621926345</v>
+        <v>56.98797904040639</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.04285877509288</v>
+        <v>17.16300388577919</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2211069773995189</v>
+        <v>4.877069088007528</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.2380513728452182</v>
+        <v>0.4900027713477177</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9105</v>
+        <v>8472</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>696.7071553615289</v>
+        <v>707.208206471732</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.56435525752401</v>
+        <v>58.39437621926345</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>48.0101690808138</v>
+        <v>30.04285877509288</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.405496945660656</v>
+        <v>0.2211069773995189</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>1</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.1839854599625436</v>
+        <v>-0.2380513728452182</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8488</v>
+        <v>9105</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>690.2275807106651</v>
+        <v>696.7071553615289</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.81809977415093</v>
+        <v>56.56435525752401</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10.94466525671975</v>
+        <v>48.0101690808138</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4883271954444426</v>
+        <v>0.405496945660656</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0433367337310002</v>
+        <v>-0.1839854599625436</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8499</v>
+        <v>8488</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>667.6239084636157</v>
+        <v>690.2275807106651</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>303.5</v>
+        <v>10.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.15753595167065</v>
+        <v>52.81809977415093</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.8807270067596</v>
+        <v>10.94466525671975</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5340195138030264</v>
+        <v>0.4883271954444426</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.5350108756488268</v>
+        <v>0.0433367337310002</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8438</v>
+        <v>8499</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>655.007981404072</v>
+        <v>667.6239084636157</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>88.2</v>
+        <v>303.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>53.78035940678302</v>
+        <v>55.15753595167065</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13.79226502994437</v>
+        <v>14.8807270067596</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.983900214119964</v>
+        <v>0.5340195138030264</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.1353690247639454</v>
+        <v>-0.5350108756488268</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8097</v>
+        <v>8438</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>651.0291670882107</v>
+        <v>655.007981404072</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>58.7</v>
+        <v>88.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.2259008697801</v>
+        <v>53.78035940678302</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.86151964770093</v>
+        <v>13.79226502994437</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2531042030466656</v>
+        <v>2.983900214119964</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.191250942818381</v>
+        <v>-0.1353690247639454</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8076</v>
+        <v>8097</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>649.1985738502556</v>
+        <v>651.0291670882107</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>25.55</v>
+        <v>58.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>50.24381474519765</v>
+        <v>56.2259008697801</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.54036782091557</v>
+        <v>26.86151964770093</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4143503942939308</v>
+        <v>0.2531042030466656</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1371507540745619</v>
+        <v>-0.191250942818381</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8069</v>
+        <v>8076</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>648.7500174741297</v>
+        <v>649.1985738502556</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>198.5</v>
+        <v>25.55</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>48.02398089703589</v>
+        <v>50.24381474519765</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.19237545159836</v>
+        <v>23.54036782091557</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6131138130313576</v>
+        <v>0.4143503942939308</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-4.768436102454655</v>
+        <v>-0.1371507540745619</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8064</v>
+        <v>8069</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>646.2504042453364</v>
+        <v>648.7500174741297</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>154</v>
+        <v>198.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.55063407817636</v>
+        <v>48.02398089703589</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>36.94455926231709</v>
+        <v>25.19237545159836</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.070153589236814</v>
+        <v>0.6131138130313576</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-3.022856258328881</v>
+        <v>-4.768436102454655</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8464</v>
+        <v>8064</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>643.1071306354239</v>
+        <v>646.2504042453364</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>349.5</v>
+        <v>154</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>61.16418551601505</v>
+        <v>59.55063407817636</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.52523929647352</v>
+        <v>36.94455926231709</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8706522539808186</v>
+        <v>1.070153589236814</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>4.236673314601442</v>
+        <v>-3.022856258328881</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>9905</v>
+        <v>8464</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>639.3326354111282</v>
+        <v>643.1071306354239</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>21.05</v>
+        <v>349.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.77401140328697</v>
+        <v>61.16418551601505</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.49098537440596</v>
+        <v>20.52523929647352</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6135698506586744</v>
+        <v>0.8706522539808186</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0602401999421298</v>
+        <v>4.236673314601442</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8341</v>
+        <v>9905</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>631.5733337206439</v>
+        <v>639.3326354111282</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>79.8</v>
+        <v>21.05</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>60.46842866660524</v>
+        <v>57.77401140328697</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>27.536804456646</v>
+        <v>17.49098537440596</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7472769880356182</v>
+        <v>0.6135698506586744</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2145905626416253</v>
+        <v>0.0602401999421298</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8150</v>
+        <v>8341</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>619.058240267202</v>
+        <v>631.5733337206439</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>94.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>53.55424943252088</v>
+        <v>60.46842866660524</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>26.95883514461168</v>
+        <v>27.536804456646</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4863031818676076</v>
+        <v>0.7472769880356182</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.9509109347480856</v>
+        <v>0.2145905626416253</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8182</v>
+        <v>8150</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>616.4851012778827</v>
+        <v>619.058240267202</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>51.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.57218319291242</v>
+        <v>53.55424943252088</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.33949473393416</v>
+        <v>26.95883514461168</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4508450254367767</v>
+        <v>0.4863031818676076</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.4060508489230505</v>
+        <v>-0.9509109347480856</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8374</v>
+        <v>8182</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>613.1488709018125</v>
+        <v>616.4851012778827</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>90.2</v>
+        <v>51.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>44.72238315509688</v>
+        <v>59.57218319291242</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.55965671394593</v>
+        <v>28.33949473393416</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.1471935127715432</v>
+        <v>0.4508450254367767</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.912237547911027</v>
+        <v>0.4060508489230505</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8162</v>
+        <v>8374</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>598.3265662749379</v>
+        <v>613.1488709018125</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>72.3</v>
+        <v>90.2</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.1046305234187</v>
+        <v>44.72238315509688</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>40.2486130324027</v>
+        <v>20.55965671394593</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4566548033005444</v>
+        <v>0.1471935127715432</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.964656534421529</v>
+        <v>-1.912237547911027</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8105</v>
+        <v>8162</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>597.9655635660334</v>
+        <v>598.3265662749379</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>21.4</v>
+        <v>72.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>63.35330399461262</v>
+        <v>58.1046305234187</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>41.18444059550372</v>
+        <v>40.2486130324027</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5275081548721166</v>
+        <v>0.4566548033005444</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0481565733128035</v>
+        <v>-0.964656534421529</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8068</v>
+        <v>8105</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>594.577901482099</v>
+        <v>597.9655635660334</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19.15</v>
+        <v>21.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>40.7155047141428</v>
+        <v>63.35330399461262</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.49919180453464</v>
+        <v>41.18444059550372</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9118532127296114</v>
+        <v>0.5275081548721166</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0158094578616179</v>
+        <v>0.0481565733128035</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8089</v>
+        <v>8068</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>591.1421497936465</v>
+        <v>594.577901482099</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>21.85</v>
+        <v>19.15</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.74741210152188</v>
+        <v>40.7155047141428</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>32.27766689392119</v>
+        <v>23.49919180453464</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.414214979364645</v>
+        <v>0.9118532127296114</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1287497167207072</v>
+        <v>0.0158094578616179</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8481</v>
+        <v>8089</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>586.7270468692238</v>
+        <v>591.1421497936465</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>42.15</v>
+        <v>21.85</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>66.15164706435996</v>
+        <v>56.74741210152188</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>27.77599425194952</v>
+        <v>32.27766689392119</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.317940220460896</v>
+        <v>1.414214979364645</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1594102873955558</v>
+        <v>0.1287497167207072</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8049</v>
+        <v>8481</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>582.2959377903182</v>
+        <v>586.7270468692238</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>27.6</v>
+        <v>42.15</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>61.2188098048773</v>
+        <v>66.15164706435996</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.58152227279967</v>
+        <v>27.77599425194952</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8268548235613439</v>
+        <v>1.317940220460896</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0598073142103737</v>
+        <v>0.1594102873955558</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8390</v>
+        <v>8049</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>579.0253073802336</v>
+        <v>582.2959377903182</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>113</v>
+        <v>27.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.20187884864713</v>
+        <v>61.2188098048773</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>29.61891532922424</v>
+        <v>24.58152227279967</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2994979016481605</v>
+        <v>0.8268548235613439</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-2.030818890048431</v>
+        <v>0.0598073142103737</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8476</v>
+        <v>8390</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>568.9744482987674</v>
+        <v>579.0253073802336</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>19.8</v>
+        <v>113</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>76.820362901664</v>
+        <v>48.20187884864713</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>42.49415477188165</v>
+        <v>29.61891532922424</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6974448298767437</v>
+        <v>0.2994979016481605</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.4879065903836804</v>
+        <v>-2.030818890048431</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8050</v>
+        <v>8476</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>563.3555686520259</v>
+        <v>568.9744482987674</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>54.9</v>
+        <v>19.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.60923694629132</v>
+        <v>76.820362901664</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45.77438201439886</v>
+        <v>42.49415477188165</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4028916284672727</v>
+        <v>0.6974448298767437</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.7742728593669197</v>
+        <v>0.4879065903836804</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>9103</v>
+        <v>8050</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>562.447907977361</v>
+        <v>563.3555686520259</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>5.33</v>
+        <v>54.9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.3855772403114</v>
+        <v>51.60923694629132</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>34.82247114151993</v>
+        <v>45.77438201439886</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5894435543494577</v>
+        <v>0.4028916284672727</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0554684133541136</v>
+        <v>-0.7742728593669197</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8114</v>
+        <v>9103</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>559.883182640113</v>
+        <v>562.447907977361</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>209</v>
+        <v>5.33</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.01493832606397</v>
+        <v>48.3855772403114</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.55404845610148</v>
+        <v>34.82247114151993</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.647904214554894</v>
+        <v>0.5894435543494577</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-5.171857923048394</v>
+        <v>-0.0554684133541136</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8271</v>
+        <v>8114</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>545.0156449641647</v>
+        <v>559.883182640113</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>208.5</v>
+        <v>209</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.19145838801814</v>
+        <v>44.01493832606397</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.4090568121342</v>
+        <v>28.55404845610148</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2880088454953067</v>
+        <v>0.647904214554894</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-4.176579990133893</v>
+        <v>-5.171857923048394</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8109</v>
+        <v>8271</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>526.7389507208454</v>
+        <v>545.0156449641647</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>118.5</v>
+        <v>208.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.77107026345043</v>
+        <v>44.19145838801814</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25.03151982262951</v>
+        <v>22.4090568121342</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1498393871746779</v>
+        <v>0.2880088454953067</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.7551468780231356</v>
+        <v>-4.176579990133893</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>9912</v>
+        <v>8109</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>526.5751571343274</v>
+        <v>526.7389507208454</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>12.6</v>
+        <v>118.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.50291733888798</v>
+        <v>47.77107026345043</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.27151930977806</v>
+        <v>25.03151982262951</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2575157134327427</v>
+        <v>0.1498393871746779</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0054313844747015</v>
+        <v>-0.7551468780231356</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8299</v>
+        <v>9912</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>526.0807494179594</v>
+        <v>526.5751571343274</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2330</v>
+        <v>12.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.5818638695609</v>
+        <v>54.50291733888798</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.2310589814731</v>
+        <v>21.27151930977806</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6018324792764376</v>
+        <v>0.2575157134327427</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-39.76797477405548</v>
+        <v>0.0054313844747015</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8072</v>
+        <v>8299</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>512.9352825979162</v>
+        <v>526.0807494179594</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>28.9</v>
+        <v>2330</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.19339440838409</v>
+        <v>48.5818638695609</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.71120861374957</v>
+        <v>16.2310589814731</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2388860669292913</v>
+        <v>0.6018324792764376</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0234069007723834</v>
+        <v>-39.76797477405548</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>9904</v>
+        <v>8277</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>510.2116442180737</v>
+        <v>524.5366157316079</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>26.45</v>
+        <v>10.35</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.75469631238646</v>
+        <v>60.51116875863421</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.03863816154868</v>
+        <v>33.56429241878752</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.039908080646068</v>
+        <v>0.579855565923592</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0899863042067342</v>
+        <v>-0.020489729510007</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8201</v>
+        <v>8072</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>509.5743417394057</v>
+        <v>512.9352825979162</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>13.7</v>
+        <v>28.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.99350117041779</v>
+        <v>53.19339440838409</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.81828223080587</v>
+        <v>22.71120861374957</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4416057844277641</v>
+        <v>0.2388860669292913</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>1</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0190731840063036</v>
+        <v>-0.0234069007723834</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8102</v>
+        <v>9904</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>496.9663281833334</v>
+        <v>510.2116442180737</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>69.8</v>
+        <v>26.45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.65448734016693</v>
+        <v>52.75469631238646</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.66550687514649</v>
+        <v>19.03863816154868</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.0979979262757428</v>
+        <v>1.039908080646068</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.7743234075968912</v>
+        <v>0.0899863042067342</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8093</v>
+        <v>8201</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>489.7460140999117</v>
+        <v>509.5743417394057</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>19.05</v>
+        <v>13.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.38653186527237</v>
+        <v>54.99350117041779</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8.805311449803463</v>
+        <v>22.81828223080587</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.065120732395105</v>
+        <v>0.4416057844277641</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.358172997921972</v>
+        <v>-0.0190731840063036</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8074</v>
+        <v>8102</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>488.5011191952254</v>
+        <v>496.9663281833334</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.97943861045899</v>
+        <v>49.65448734016693</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10.78435150378618</v>
+        <v>12.66550687514649</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.951905073908048</v>
+        <v>0.0979979262757428</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.046444421533933</v>
+        <v>-0.7743234075968912</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8462</v>
+        <v>8093</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>482.4131319293126</v>
+        <v>489.7460140999117</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>144.5</v>
+        <v>19.05</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>56.70533061091922</v>
+        <v>52.38653186527237</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.43628477958876</v>
+        <v>8.805311449803463</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.918205263371606</v>
+        <v>1.065120732395105</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.7863793701294238</v>
+        <v>0.358172997921972</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>9910</v>
+        <v>8074</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>478.8064364885111</v>
+        <v>488.5011191952254</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>72.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.01073370943084</v>
+        <v>50.97943861045899</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>27.04400936665104</v>
+        <v>10.78435150378618</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6992030059635206</v>
+        <v>0.951905073908048</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2643427109227465</v>
+        <v>0.046444421533933</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>9907</v>
+        <v>8462</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>470.9353655603979</v>
+        <v>482.4131319293126</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>16.65</v>
+        <v>144.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.61103232099885</v>
+        <v>56.70533061091922</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.99202744288766</v>
+        <v>15.43628477958876</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.89866657321818</v>
+        <v>1.918205263371606</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0895003105667448</v>
+        <v>0.7863793701294238</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8429</v>
+        <v>9910</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>468.6691000050145</v>
+        <v>478.8064364885111</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>6.67</v>
+        <v>72.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>57.64162832413053</v>
+        <v>44.01073370943084</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27.68878070166491</v>
+        <v>27.04400936665104</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3314801995978744</v>
+        <v>0.6992030059635206</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0343371144784113</v>
+        <v>-0.2643427109227465</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8455</v>
+        <v>9907</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>467.2869174728148</v>
+        <v>470.9353655603979</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>31.05</v>
+        <v>16.65</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.28283157613561</v>
+        <v>50.61103232099885</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>24.36892939110867</v>
+        <v>22.99202744288766</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.414460358778502</v>
+        <v>1.89866657321818</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-1.236838359606019</v>
+        <v>0.0895003105667448</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8210</v>
+        <v>8429</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>460.5733744064629</v>
+        <v>468.6691000050145</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1345</v>
+        <v>6.67</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.96776046958171</v>
+        <v>57.64162832413053</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.24796110452932</v>
+        <v>27.68878070166491</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5039443314524061</v>
+        <v>0.3314801995978744</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>1</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-16.81192091132851</v>
+        <v>0.0343371144784113</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8067</v>
+        <v>8455</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>449.7378707385388</v>
+        <v>467.2869174728148</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>12.55</v>
+        <v>31.05</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.20354359640426</v>
+        <v>45.28283157613561</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6.819110756400955</v>
+        <v>24.36892939110867</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2455537277298404</v>
+        <v>0.414460358778502</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1816936015146128</v>
+        <v>-1.236838359606019</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8477</v>
+        <v>8210</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>448.423578404673</v>
+        <v>460.5733744064629</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>16.8</v>
+        <v>1345</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.08218717856963</v>
+        <v>47.96776046958171</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.36816392697481</v>
+        <v>23.24796110452932</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2338685912833209</v>
+        <v>0.5039443314524061</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>1</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.4571447161295652</v>
+        <v>-16.81192091132851</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8087</v>
+        <v>8067</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>448.0089386208688</v>
+        <v>449.7378707385388</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>33.55</v>
+        <v>12.55</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.99050532006213</v>
+        <v>50.20354359640426</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.67275495717216</v>
+        <v>6.819110756400955</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2783530111697406</v>
+        <v>0.2455537277298404</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1587343787633785</v>
+        <v>-0.1816936015146128</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8422</v>
+        <v>8477</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>446.5213090878483</v>
+        <v>448.423578404673</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>28.45</v>
+        <v>16.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.00156422091254</v>
+        <v>46.08218717856963</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.83288626699832</v>
+        <v>29.36816392697481</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.500960203739105</v>
+        <v>0.2338685912833209</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1155268585295996</v>
+        <v>-0.4571447161295652</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>9110</v>
+        <v>8087</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>445.385107140035</v>
+        <v>448.0089386208688</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>3.5</v>
+        <v>33.55</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>57.92938281792336</v>
+        <v>45.99050532006213</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.91133930033816</v>
+        <v>21.67275495717216</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.1710091746422195</v>
+        <v>0.2783530111697406</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0050254127448788</v>
+        <v>-0.1587343787633785</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8111</v>
+        <v>8422</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>439.7027400210145</v>
+        <v>446.5213090878483</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>54.5</v>
+        <v>28.45</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>31.62948809991182</v>
+        <v>52.00156422091254</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26.60963286251742</v>
+        <v>16.83288626699832</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6396837459794882</v>
+        <v>0.500960203739105</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.7532880361996774</v>
+        <v>0.1155268585295996</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>9930</v>
+        <v>9110</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>435.5858614808737</v>
+        <v>445.385107140035</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>57.50456142501539</v>
+        <v>57.92938281792336</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.19954303206696</v>
+        <v>16.91133930033816</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7749703444113674</v>
+        <v>0.1710091746422195</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1518184370530271</v>
+        <v>0.0050254127448788</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8103</v>
+        <v>8111</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>428.4632991491391</v>
+        <v>439.7027400210145</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>40.15742379194598</v>
+        <v>31.62948809991182</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.12530739632136</v>
+        <v>26.60963286251742</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6782651957694246</v>
+        <v>0.6396837459794882</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>1</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-1.049511746577202</v>
+        <v>-0.7532880361996774</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8466</v>
+        <v>9930</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>422.9039644348239</v>
+        <v>435.5858614808737</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>15.9</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.16343959994324</v>
+        <v>57.50456142501539</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.96054092135193</v>
+        <v>13.19954303206696</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2428446077082667</v>
+        <v>0.7749703444113674</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0620785617833004</v>
+        <v>0.1518184370530271</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8240</v>
+        <v>8103</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>421.7946531165105</v>
+        <v>428.4632991491391</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>56.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>39.19837837001397</v>
+        <v>40.15742379194598</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>17.82758642422184</v>
+        <v>20.12530739632136</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3797985847865558</v>
+        <v>0.6782651957694246</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.6049325132175918</v>
+        <v>-1.049511746577202</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8487</v>
+        <v>8466</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>420.4511379115914</v>
+        <v>422.9039644348239</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>79.3</v>
+        <v>15.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.88638571783257</v>
+        <v>50.16343959994324</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.52265112234852</v>
+        <v>21.96054092135193</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4951364043568552</v>
+        <v>0.2428446077082667</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.14250040581497</v>
+        <v>0.0620785617833004</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8227</v>
+        <v>8240</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>409.5596834246998</v>
+        <v>421.7946531165105</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>182.5</v>
+        <v>56.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.2414733843353</v>
+        <v>39.19837837001397</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25.54621886393356</v>
+        <v>17.82758642422184</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2938514459111908</v>
+        <v>0.3797985847865558</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-4.987670243556359</v>
+        <v>-0.6049325132175918</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>9902</v>
+        <v>8487</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>392.4828402625715</v>
+        <v>420.4511379115914</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>13.75</v>
+        <v>79.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.37613180537004</v>
+        <v>47.88638571783257</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.90944608654138</v>
+        <v>18.52265112234852</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5097155815551955</v>
+        <v>0.4951364043568552</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0017792305173537</v>
+        <v>-0.14250040581497</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8176</v>
+        <v>8227</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>389.2419748991014</v>
+        <v>409.5596834246998</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>10.1</v>
+        <v>182.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.06723160134877</v>
+        <v>45.2414733843353</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9.162106109333919</v>
+        <v>25.54621886393356</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.194148764144726</v>
+        <v>0.2938514459111908</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0024891349146017</v>
+        <v>-4.987670243556359</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8383</v>
+        <v>9902</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>388.6894707014939</v>
+        <v>392.4828402625715</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>60.1</v>
+        <v>13.75</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>52.22840175793417</v>
+        <v>45.37613180537004</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.89358642624375</v>
+        <v>13.90944608654138</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4937122289194783</v>
+        <v>0.5097155815551955</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0409750180334401</v>
+        <v>-0.0017792305173537</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8085</v>
+        <v>8291</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>385.6947110969282</v>
+        <v>391.9951427983745</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>13.05</v>
+        <v>43.1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.95603957738257</v>
+        <v>38.99011204690771</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>24.1430530087661</v>
+        <v>31.1284219669371</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.648404473297034</v>
+        <v>0.447898106719285</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0020748784997166</v>
+        <v>-7.907564175620996</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8147</v>
+        <v>8176</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>384.412303320603</v>
+        <v>389.2419748991014</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>147</v>
+        <v>10.1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>40.20155658717184</v>
+        <v>45.06723160134877</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>21.77862622228772</v>
+        <v>9.162106109333919</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3281587278408378</v>
+        <v>1.194148764144726</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-2.721963175283904</v>
+        <v>0.0024891349146017</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8101</v>
+        <v>8383</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>379.4308168787883</v>
+        <v>388.6894707014939</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>14.2</v>
+        <v>60.1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.68941501334832</v>
+        <v>52.22840175793417</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.62362905949321</v>
+        <v>15.89358642624375</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7681313333802615</v>
+        <v>0.4937122289194783</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1198013398115346</v>
+        <v>-0.0409750180334401</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>9908</v>
+        <v>8085</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>361.2128915804353</v>
+        <v>385.6947110969282</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>29.65</v>
+        <v>13.05</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>59.10244276587163</v>
+        <v>50.95603957738257</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.33608937351665</v>
+        <v>24.1430530087661</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.572026886248826</v>
+        <v>0.648404473297034</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0623083046791604</v>
+        <v>0.0020748784997166</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8404</v>
+        <v>8147</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>339.8215556619286</v>
+        <v>384.412303320603</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>16.75</v>
+        <v>147</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.24116769735276</v>
+        <v>40.20155658717184</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.91151228792523</v>
+        <v>21.77862622228772</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4541337952068335</v>
+        <v>0.3281587278408378</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0005627694738732</v>
+        <v>-2.721963175283904</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8442</v>
+        <v>8101</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>333.5074124682333</v>
+        <v>379.4308168787883</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.25</v>
+        <v>14.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>35.48881546568923</v>
+        <v>47.68941501334832</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>23.17218338789122</v>
+        <v>16.62362905949321</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3175116232770029</v>
+        <v>0.7681313333802615</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.4272651198189408</v>
+        <v>-0.1198013398115346</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>9955</v>
+        <v>9908</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>327.9382815674693</v>
+        <v>361.2128915804353</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>27.3</v>
+        <v>29.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.77381519783385</v>
+        <v>59.10244276587163</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.2541201358193</v>
+        <v>14.33608937351665</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5530810709499764</v>
+        <v>0.572026886248826</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0115916494955105</v>
+        <v>0.0623083046791604</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8463</v>
+        <v>8404</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>296.6258635061345</v>
+        <v>339.8215556619286</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>22.1</v>
+        <v>16.75</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.55311567351517</v>
+        <v>44.24116769735276</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.61293115136882</v>
+        <v>14.91151228792523</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.765276676173279</v>
+        <v>0.4541337952068335</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0709551925244227</v>
+        <v>0.0005627694738732</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>9911</v>
+        <v>8442</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>292.3278904253873</v>
+        <v>333.5074124682333</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>40.25</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.39045627808968</v>
+        <v>35.48881546568923</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.51385312202772</v>
+        <v>23.17218338789122</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5997054824247887</v>
+        <v>0.3175116232770029</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0192052678488822</v>
+        <v>0.4272651198189408</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8222</v>
+        <v>9955</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>290.3893728449298</v>
+        <v>327.9382815674693</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>35.55</v>
+        <v>27.3</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.07231415647936</v>
+        <v>43.77381519783385</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.84885986716123</v>
+        <v>22.2541201358193</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4626072133226314</v>
+        <v>0.5530810709499764</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1103553205427085</v>
+        <v>-0.0115916494955105</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8249</v>
+        <v>8463</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>286.2638187895933</v>
+        <v>296.6258635061345</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>53</v>
+        <v>22.1</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.33222744512143</v>
+        <v>51.55311567351517</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20.69954357109324</v>
+        <v>12.61293115136882</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.132933332274709</v>
+        <v>1.765276676173279</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.259768978709037</v>
+        <v>0.0709551925244227</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8940</v>
+        <v>9911</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>269.239549364398</v>
+        <v>292.3278904253873</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>16.6</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.37089638252834</v>
+        <v>45.39045627808968</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11.74537789244157</v>
+        <v>16.51385312202772</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.026838325752412</v>
+        <v>0.5997054824247887</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0406320375538965</v>
+        <v>0.0192052678488822</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8478</v>
+        <v>8222</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>266.9154977518612</v>
+        <v>290.3893728449298</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>152</v>
+        <v>35.55</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42.87614339735063</v>
+        <v>49.07231415647936</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.2240080651398</v>
+        <v>13.84885986716123</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4297746020020345</v>
+        <v>0.4626072133226314</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2409539976232886</v>
+        <v>-0.1103553205427085</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8443</v>
+        <v>8249</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>266.1115494584557</v>
+        <v>286.2638187895933</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>11.4</v>
+        <v>53</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.28717668737792</v>
+        <v>52.33222744512143</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>57.06536787925178</v>
+        <v>20.69954357109324</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4629864454750212</v>
+        <v>1.132933332274709</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0327077609737427</v>
+        <v>-0.259768978709037</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8482</v>
+        <v>8940</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>265.5330187451853</v>
+        <v>269.239549364398</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>48.75</v>
+        <v>16.6</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.73424846018784</v>
+        <v>44.37089638252834</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>5.547529606602443</v>
+        <v>11.74537789244157</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9752054026379308</v>
+        <v>1.026838325752412</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.7020657631679174</v>
+        <v>0.0406320375538965</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8410</v>
+        <v>8478</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>259.7689237510695</v>
+        <v>266.9154977518612</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>32.9</v>
+        <v>152</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>34.80289441191468</v>
+        <v>42.87614339735063</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.50479648156353</v>
+        <v>17.2240080651398</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3.376892375106952</v>
+        <v>0.4297746020020345</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1180980549683087</v>
+        <v>-0.2409539976232886</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8932</v>
+        <v>8443</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>250.4358671614074</v>
+        <v>266.1115494584557</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>100</v>
+        <v>11.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.07670995244992</v>
+        <v>48.28717668737792</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.7734463441373</v>
+        <v>57.06536787925178</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4732415300335199</v>
+        <v>0.4629864454750212</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1929277423408621</v>
+        <v>0.0327077609737427</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8423</v>
+        <v>8482</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>243.9280344064514</v>
+        <v>265.5330187451853</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>17.75</v>
+        <v>48.75</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>47.42774790064275</v>
+        <v>51.73424846018784</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.74145584293808</v>
+        <v>5.547529606602443</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2165905715595091</v>
+        <v>0.9752054026379308</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0186003832063409</v>
+        <v>0.7020657631679174</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8234</v>
+        <v>8410</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>236.7560613955521</v>
+        <v>259.7689237510695</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>63.8</v>
+        <v>32.9</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.62931694858379</v>
+        <v>34.80289441191468</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>19.12234220610412</v>
+        <v>20.50479648156353</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2626509719183666</v>
+        <v>3.376892375106952</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.7867319082144344</v>
+        <v>-0.1180980549683087</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8092</v>
+        <v>8932</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>236.0430761213945</v>
+        <v>250.4358671614074</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>14.6</v>
+        <v>100</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>34.54906485945281</v>
+        <v>50.07670995244992</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>20.59875322897995</v>
+        <v>16.7734463441373</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2493299785570875</v>
+        <v>0.4732415300335199</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3074168270061911</v>
+        <v>-0.1929277423408621</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8171</v>
+        <v>8423</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>220.5801678106944</v>
+        <v>243.9280344064514</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>21.55</v>
+        <v>17.75</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.36568743997213</v>
+        <v>47.42774790064275</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.50922265951933</v>
+        <v>12.74145584293808</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8617664383175869</v>
+        <v>0.2165905715595091</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.338262479269563</v>
+        <v>0.0186003832063409</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8080</v>
+        <v>8234</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>195.4192198702228</v>
+        <v>236.7560613955521</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>27.95</v>
+        <v>63.8</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.46821469749827</v>
+        <v>43.62931694858379</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>41.55494484533417</v>
+        <v>19.12234220610412</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8982665170740957</v>
+        <v>0.2626509719183666</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.050671804079677</v>
+        <v>-0.7867319082144344</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8054</v>
+        <v>8092</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>190.7261938122678</v>
+        <v>236.0430761213945</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.60798140216314</v>
+        <v>34.54906485945281</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.26257319755103</v>
+        <v>20.59875322897995</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3262760434647563</v>
+        <v>0.2493299785570875</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.3235834156083355</v>
+        <v>-0.3074168270061911</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8213</v>
+        <v>8171</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>190.4573576423961</v>
+        <v>220.5801678106944</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>36.5</v>
+        <v>21.55</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.28972948498662</v>
+        <v>40.36568743997213</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.74658284346117</v>
+        <v>18.50922265951933</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2573248637384617</v>
+        <v>0.8617664383175869</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1794994509226068</v>
+        <v>-0.338262479269563</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9802</v>
+        <v>8080</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>190.1371728701898</v>
+        <v>195.4192198702228</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>27.95</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.24681186745618</v>
+        <v>47.46821469749827</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.86801675632422</v>
+        <v>41.55494484533417</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4246133371401908</v>
+        <v>0.8982665170740957</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0304060194919026</v>
+        <v>0.050671804079677</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8367</v>
+        <v>8054</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>182.5304563416982</v>
+        <v>190.7261938122678</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>40.4</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>36.79979151928478</v>
+        <v>42.60798140216314</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>24.69199119652605</v>
+        <v>11.26257319755103</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6303638585610506</v>
+        <v>0.3262760434647563</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0470758766894556</v>
+        <v>-0.3235834156083355</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8183</v>
+        <v>8213</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>175.1428078292441</v>
+        <v>190.4573576423961</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>32.75</v>
+        <v>36.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>52.67220892334547</v>
+        <v>47.28972948498662</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.90881194087629</v>
+        <v>15.74658284346117</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.2718213964062031</v>
+        <v>0.2573248637384617</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1814351331184597</v>
+        <v>-0.1794994509226068</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8440</v>
+        <v>9802</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>124.7539330012465</v>
+        <v>190.1371728701898</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>22.25</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.57976613151376</v>
+        <v>48.24681186745618</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.74680286659082</v>
+        <v>13.86801675632422</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.1705787028335516</v>
+        <v>0.4246133371401908</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>1</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1247672442679963</v>
+        <v>0.0304060194919026</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8467</v>
+        <v>8367</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>114.3829645467552</v>
+        <v>182.5304563416982</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>126</v>
+        <v>40.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.50700173891659</v>
+        <v>36.79979151928478</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.41468496003622</v>
+        <v>24.69199119652605</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5643894130555372</v>
+        <v>0.6303638585610506</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1425662482218532</v>
+        <v>0.0470758766894556</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8059</v>
+        <v>8183</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>106.096950712373</v>
+        <v>175.1428078292441</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17.35</v>
+        <v>32.75</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>36.44175752239637</v>
+        <v>52.67220892334547</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.60798551461076</v>
+        <v>13.90881194087629</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5359908744226293</v>
+        <v>0.2718213964062031</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,62 +6453,221 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2129002486358014</v>
+        <v>0.1814351331184597</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
+        <v>8440</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>綠電</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>124.7539330012465</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>46.57976613151376</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>14.74680286659082</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.1705787028335516</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.1247672442679963</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>8467</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>波力-KY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>114.3829645467552</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>50.50700173891659</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>19.41468496003622</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.5643894130555372</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.1425662482218532</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>8059</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>凱碩</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>106.096950712373</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>36.44175752239637</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>16.60798551461076</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5359908744226293</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.2129002486358014</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8084</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>巨虹</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>88.37341384404854</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>45.6</v>
       </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>44.00857847469421</v>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>17.51576575342806</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.7177420114774644</v>
       </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.3143006592624774</v>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
